--- a/SensitivityAnalysis/SingleSNP/MR_dat_binarySA.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_binarySA.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="48">
   <si>
     <t>SNP</t>
   </si>
@@ -70,12 +70,39 @@
     <t>outcome</t>
   </si>
   <si>
+    <t>beta_95L</t>
+  </si>
+  <si>
+    <t>beta_95U</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
     <t>pval.exposure</t>
   </si>
   <si>
+    <t>X_.log10_p.value</t>
+  </si>
+  <si>
+    <t>q_statistic</t>
+  </si>
+  <si>
+    <t>q_p.value</t>
+  </si>
+  <si>
+    <t>i2</t>
+  </si>
+  <si>
+    <t>n_studies</t>
+  </si>
+  <si>
     <t>N.exposure</t>
   </si>
   <si>
+    <t>effects</t>
+  </si>
+  <si>
     <t>se.exposure</t>
   </si>
   <si>
@@ -85,9 +112,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -113,6 +137,9 @@
   </si>
   <si>
     <t>Fracture</t>
+  </si>
+  <si>
+    <t>+++</t>
   </si>
   <si>
     <t>Sclerostin</t>
@@ -261,25 +288,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -294,16 +345,16 @@
         <v>0.4161272294010711</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O2" t="n">
         <v>0.01592154796470022</v>
@@ -315,33 +366,57 @@
         <v>325648.0</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -435,25 +510,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -468,16 +567,16 @@
         <v>0.41612937889533635</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O2" t="n">
         <v>0.016473902544292388</v>
@@ -489,33 +588,57 @@
         <v>325710.0</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -609,25 +732,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -642,16 +789,16 @@
         <v>0.4161424385209394</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.020645891525153566</v>
@@ -663,33 +810,57 @@
         <v>325558.0</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -783,25 +954,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -816,16 +1011,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>0.032476512562888055</v>
@@ -837,33 +1032,57 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -957,25 +1176,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -990,16 +1233,16 @@
         <v>0.41612774988418244</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>0.007529667581937513</v>
@@ -1011,33 +1254,57 @@
         <v>319468.0</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1131,25 +1398,49 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>-0.041722</v>
@@ -1164,16 +1455,16 @@
         <v>0.41622654410331617</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.01967321528235143</v>
@@ -1185,33 +1476,57 @@
         <v>312981.0</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/SensitivityAnalysis/SingleSNP/MR_dat_binarySA.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_binarySA.xlsx
@@ -333,16 +333,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0793845755854418</v>
+        <v>0.1876745017401533</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161272294010711</v>
+        <v>0.6015279342074505</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -357,13 +357,13 @@
         <v>39</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01592154796470022</v>
+        <v>0.053959776377508505</v>
       </c>
       <c r="P2" t="n">
-        <v>6.16474030027964E-7</v>
+        <v>5.050861259054416E-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>325648.0</v>
+        <v>235285.0</v>
       </c>
       <c r="R2" t="s">
         <v>39</v>
@@ -555,16 +555,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02137471960785234</v>
+        <v>-0.03256545567730134</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41612937889533635</v>
+        <v>0.6019522868197408</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -579,13 +579,13 @@
         <v>43</v>
       </c>
       <c r="O2" t="n">
-        <v>0.016473902544292388</v>
+        <v>0.022957985618616</v>
       </c>
       <c r="P2" t="n">
-        <v>0.19446273141300288</v>
+        <v>0.15605051823215044</v>
       </c>
       <c r="Q2" t="n">
-        <v>325710.0</v>
+        <v>236748.0</v>
       </c>
       <c r="R2" t="s">
         <v>43</v>
@@ -777,16 +777,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.024370764061687335</v>
+        <v>-0.043351908989276426</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161424385209394</v>
+        <v>0.6019910287334433</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -801,13 +801,13 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.020645891525153566</v>
+        <v>0.03481577994158205</v>
       </c>
       <c r="P2" t="n">
-        <v>0.23783435139778358</v>
+        <v>0.21306563349644525</v>
       </c>
       <c r="Q2" t="n">
-        <v>325558.0</v>
+        <v>236310.0</v>
       </c>
       <c r="R2" t="s">
         <v>44</v>
@@ -999,16 +999,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0010224074135774179</v>
+        <v>0.022349519218333835</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018797178976263</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1023,13 +1023,13 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>0.032476512562888055</v>
+        <v>0.041404230393366034</v>
       </c>
       <c r="P2" t="n">
-        <v>0.974885592758964</v>
+        <v>0.5893430353599408</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>241898.0</v>
       </c>
       <c r="R2" t="s">
         <v>45</v>
@@ -1221,16 +1221,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.005479769427927969</v>
+        <v>-0.01247889220385636</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41612774988418244</v>
+        <v>0.6019620558259113</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1245,13 +1245,13 @@
         <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007529667581937513</v>
+        <v>0.015701121684102908</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4667622585995815</v>
+        <v>0.4267431650463671</v>
       </c>
       <c r="Q2" t="n">
-        <v>319468.0</v>
+        <v>174256.0</v>
       </c>
       <c r="R2" t="s">
         <v>46</v>
@@ -1443,16 +1443,16 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04159828723565264</v>
+        <v>-0.03585864896824078</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41622654410331617</v>
+        <v>0.6019778124685706</v>
       </c>
       <c r="K2" t="s">
         <v>38</v>
@@ -1467,13 +1467,13 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01967321528235143</v>
+        <v>0.02859319991141303</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03447573552661242</v>
+        <v>0.20980671585189614</v>
       </c>
       <c r="Q2" t="n">
-        <v>312981.0</v>
+        <v>228687.0</v>
       </c>
       <c r="R2" t="s">
         <v>47</v>
